--- a/servers/maze_main_server_dev/conf.d/data/maze_shop_equip_list_v8【迷宫-商店购买装备队列】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_shop_equip_list_v8【迷宫-商店购买装备队列】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4850A5C0-C90C-4E02-8E3C-FFC7A583C4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C091EB-7432-4719-9DD5-B48B19A7EFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B965FE27-C998-4B23-9CF9-52FD9DD9A018}"/>
   </bookViews>
@@ -282,12 +282,6 @@
     <t>8040000</t>
   </si>
   <si>
-    <t>42618001,42633001,42614001,42657001,42636001,42615001,42618001,42634001,42617001,42656001,42612001,42615001,42638001,42614001,42617001,42731001,42612001,42658001,42616001,42617001,42731001,42612001,42633001,42616001,42711001,42632001,42613001,42616001,42635001,42618001,42652001,42617001,42613001,42636001,42615001,42618001,42634001,42617001,42655001,42711001,42632001,42613001,42616001,42635001,42618001,42654001,42617001,42613001,42636001,42615001,42618001,42634001,42617001,42751001,42612001,42615001,42638001,42614001,42617001,42731001,42612001,42653001,42616001</t>
-  </si>
-  <si>
-    <t>42613001,42617001,42633001,42618001,42612001,42636001</t>
-  </si>
-  <si>
     <t>42711002,42632002,42613002,42616002,42635002,42618002,42654002,42617002,42613002,42636002,42615002,42618002,42634002,42617002,42751002,42612002,42615002,42638002,42614002,42617002,42731002,42612002,42653002,42616002,42711002,42632002,42613002,42616002,42635002,42614002,42658002,42617002,42613002,42636002,42615002,42618002,42634002,42711002,42657002,42612002,42615002,42638002,42614002,42617002,42731002,42612002,42656002,42613002,42711002,42632002,42613002,42616002,42634002,42618002,42655002,42617002,42613002,42636002,42615002,42618002,42634002,42617002,42652002,42711002</t>
   </si>
   <si>
@@ -313,6 +307,12 @@
   </si>
   <si>
     <t>42711008,42632008,42613008,42616008,42635008,42618008,42654008,42617008,42613008,42636008,42615008,42618008,42634008,42617008,42751008,42612008,42615008,42638008,42614008,42617008,42731008,42612008,42663008,42616008,42711008,42632008,42613008,42616008,42635008,42614008,42658008,42617008,42613008,42636008,42655008,42668008,42634008,42711008,42657008,42612008,42615008,42638008,42654008,42667008,42731008,42612008,42656008,42613008,42711008,42632008,42613008,42616008,42634008,42618008,42655008,42617008,42613008,42636008,42615008,42618008,42634008,42617008,42652008,42711008</t>
+  </si>
+  <si>
+    <t>42618001,42633001,42614001,42657001,42636001,42615001,42618001,42634001,42617001,42656001,42612001,42615001,42638001,42614001,42617001,42731001,42612001,42658001,42616001,42617001,42731001,42612001,42633001,42616001</t>
+  </si>
+  <si>
+    <t>42633001,42617001,42616001,42618001,42632001,42615001</t>
   </si>
 </sst>
 </file>
@@ -793,7 +793,7 @@
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="5" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -808,7 +808,7 @@
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="5" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -823,7 +823,7 @@
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="5" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -838,7 +838,7 @@
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="5" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -853,7 +853,7 @@
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="5" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -868,7 +868,7 @@
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -883,7 +883,7 @@
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -898,7 +898,7 @@
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -913,7 +913,7 @@
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -928,7 +928,7 @@
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -943,7 +943,7 @@
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -958,7 +958,7 @@
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -973,7 +973,7 @@
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -988,7 +988,7 @@
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1667,19 +1667,19 @@
       </c>
       <c r="B3" s="1" cm="1">
         <f t="array" aca="1" ref="B3:E3" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="C3" s="1">
         <f ca="1"/>
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="D3" s="1">
         <f ca="1"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1">
         <f ca="1"/>
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G3" s="1">
         <v>100</v>
@@ -1928,19 +1928,19 @@
       </c>
       <c r="B4" s="1" cm="1">
         <f t="array" aca="1" ref="B4:E4" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1">
         <f ca="1"/>
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1">
         <f ca="1"/>
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E4" s="1">
         <f ca="1"/>
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="G4" s="1">
         <f>G3+1</f>
@@ -2190,19 +2190,19 @@
       </c>
       <c r="B5" s="1" cm="1">
         <f t="array" aca="1" ref="B5:E5" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C5" s="1">
         <f ca="1"/>
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1">
         <f ca="1"/>
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="E5" s="1">
         <f ca="1"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5" s="1">
         <f>G4+1</f>
@@ -2452,19 +2452,19 @@
       </c>
       <c r="B6" s="1" cm="1">
         <f t="array" aca="1" ref="B6:E6" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1">
         <f ca="1"/>
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D6" s="1">
         <f ca="1"/>
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E6" s="1">
         <f ca="1"/>
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="G6" s="1">
         <f>G5+1</f>
@@ -2714,19 +2714,19 @@
       </c>
       <c r="B7" s="1" cm="1">
         <f t="array" aca="1" ref="B7:E7" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C7" s="1">
         <f ca="1"/>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="1">
         <f ca="1"/>
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="E7" s="1">
         <f ca="1"/>
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="G7" s="1">
         <f>G6+1</f>
@@ -2977,19 +2977,19 @@
       </c>
       <c r="B8" s="1" cm="1">
         <f t="array" aca="1" ref="B8:E8" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1">
         <f ca="1"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D8" s="1">
         <f ca="1"/>
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="E8" s="1">
         <f ca="1"/>
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" ref="G8:G22" si="4">G3+100</f>
@@ -3240,19 +3240,19 @@
       </c>
       <c r="B9" s="1" cm="1">
         <f t="array" aca="1" ref="B9:E9" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1">
         <f ca="1"/>
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D9" s="1">
         <f ca="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E9" s="1">
         <f ca="1"/>
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G9" s="1">
         <f t="shared" si="4"/>
@@ -3503,19 +3503,19 @@
       </c>
       <c r="B10" s="1" cm="1">
         <f t="array" aca="1" ref="B10:E10" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C10" s="1">
         <f ca="1"/>
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D10" s="1">
         <f ca="1"/>
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E10" s="1">
         <f ca="1"/>
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" si="4"/>
@@ -3766,19 +3766,19 @@
       </c>
       <c r="B11" s="1" cm="1">
         <f t="array" aca="1" ref="B11:E11" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C11" s="1">
         <f ca="1"/>
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D11" s="1">
         <f ca="1"/>
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="E11" s="1">
         <f ca="1"/>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" si="4"/>
@@ -4029,19 +4029,19 @@
       </c>
       <c r="B12" s="1" cm="1">
         <f t="array" aca="1" ref="B12:E12" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1">
         <f ca="1"/>
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D12" s="1">
         <f ca="1"/>
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E12" s="1">
         <f ca="1"/>
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="4"/>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="B13" s="1" cm="1">
         <f t="array" aca="1" ref="B13:E13" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="C13" s="1">
         <f ca="1"/>
@@ -4300,11 +4300,11 @@
       </c>
       <c r="D13" s="1">
         <f ca="1"/>
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E13" s="1">
         <f ca="1"/>
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G13" s="1">
         <f t="shared" si="4"/>
@@ -4559,15 +4559,15 @@
       </c>
       <c r="C14" s="1">
         <f ca="1"/>
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="D14" s="1">
         <f ca="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E14" s="1">
         <f ca="1"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G14" s="1">
         <f t="shared" si="4"/>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="B15" s="1" cm="1">
         <f t="array" aca="1" ref="B15:E15" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C15" s="1">
         <f ca="1"/>
@@ -4826,11 +4826,11 @@
       </c>
       <c r="D15" s="1">
         <f ca="1"/>
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E15" s="1">
         <f ca="1"/>
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" si="4"/>
@@ -5081,19 +5081,19 @@
       </c>
       <c r="B16" s="1" cm="1">
         <f t="array" aca="1" ref="B16:E16" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1">
         <f ca="1"/>
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D16" s="1">
         <f ca="1"/>
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E16" s="1">
         <f ca="1"/>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G16" s="1">
         <f t="shared" si="4"/>
@@ -5344,19 +5344,19 @@
       </c>
       <c r="B17" s="1" cm="1">
         <f t="array" aca="1" ref="B17:E17" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C17" s="1">
         <f ca="1"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D17" s="1">
         <f ca="1"/>
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E17" s="1">
         <f ca="1"/>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" si="4"/>
@@ -5607,19 +5607,19 @@
       </c>
       <c r="B18" s="1" cm="1">
         <f t="array" aca="1" ref="B18:E18" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C18" s="1">
         <f ca="1"/>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D18" s="1">
         <f ca="1"/>
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="E18" s="1">
         <f ca="1"/>
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" si="4"/>
@@ -5870,19 +5870,19 @@
       </c>
       <c r="B19" s="1" cm="1">
         <f t="array" aca="1" ref="B19:E19" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C19" s="1">
         <f ca="1"/>
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D19" s="1">
         <f ca="1"/>
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E19" s="1">
         <f ca="1"/>
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" si="4"/>
@@ -6133,19 +6133,19 @@
       </c>
       <c r="B20" s="1" cm="1">
         <f t="array" aca="1" ref="B20:E20" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C20" s="1">
         <f ca="1"/>
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D20" s="1">
         <f ca="1"/>
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="E20" s="1">
         <f ca="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" si="4"/>
@@ -6396,19 +6396,19 @@
       </c>
       <c r="B21" s="1" cm="1">
         <f t="array" aca="1" ref="B21:E21" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1">
         <f ca="1"/>
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="D21" s="1">
         <f ca="1"/>
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E21" s="1">
         <f ca="1"/>
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G21" s="1">
         <f t="shared" si="4"/>
@@ -6659,7 +6659,7 @@
       </c>
       <c r="B22" s="1" cm="1">
         <f t="array" aca="1" ref="B22:E22" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C22" s="1">
         <f ca="1"/>
@@ -6667,11 +6667,11 @@
       </c>
       <c r="D22" s="1">
         <f ca="1"/>
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E22" s="1">
         <f ca="1"/>
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="G22" s="1">
         <f t="shared" si="4"/>
@@ -6922,19 +6922,19 @@
       </c>
       <c r="B23" s="1" cm="1">
         <f t="array" aca="1" ref="B23:E23" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="C23" s="1">
         <f ca="1"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D23" s="1">
         <f ca="1"/>
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E23" s="1">
         <f ca="1"/>
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="N23" s="1">
         <v>40001</v>
@@ -7168,19 +7168,19 @@
       </c>
       <c r="B24" s="1" cm="1">
         <f t="array" aca="1" ref="B24:E24" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C24" s="1">
         <f ca="1"/>
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D24" s="1">
         <f ca="1"/>
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E24" s="1">
         <f ca="1"/>
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="N24" s="1">
         <v>40001</v>
@@ -7414,19 +7414,19 @@
       </c>
       <c r="B25" s="1" cm="1">
         <f t="array" aca="1" ref="B25:E25" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C25" s="1">
         <f ca="1"/>
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D25" s="1">
         <f ca="1"/>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E25" s="1">
         <f ca="1"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N25" s="1">
         <v>40001</v>
@@ -7660,19 +7660,19 @@
       </c>
       <c r="B26" s="1" cm="1">
         <f t="array" aca="1" ref="B26:E26" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C26" s="1">
         <f ca="1"/>
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D26" s="1">
         <f ca="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E26" s="1">
         <f ca="1"/>
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N26" s="1">
         <v>40001</v>
@@ -7906,19 +7906,19 @@
       </c>
       <c r="B27" s="1" cm="1">
         <f t="array" aca="1" ref="B27:E27" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C27" s="1">
         <f ca="1"/>
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D27" s="1">
         <f ca="1"/>
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E27" s="1">
         <f ca="1"/>
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="N27" s="1">
         <v>40001</v>
@@ -8152,19 +8152,19 @@
       </c>
       <c r="B28" s="1" cm="1">
         <f t="array" aca="1" ref="B28:E28" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C28" s="1">
         <f ca="1"/>
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D28" s="1">
         <f ca="1"/>
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E28" s="1">
         <f ca="1"/>
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="N28" s="1">
         <v>40001</v>
@@ -8398,19 +8398,19 @@
       </c>
       <c r="B29" s="1" cm="1">
         <f t="array" aca="1" ref="B29:E29" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C29" s="1">
         <f ca="1"/>
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D29" s="1">
         <f ca="1"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E29" s="1">
         <f ca="1"/>
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="N29" s="1">
         <v>40001</v>
@@ -8644,19 +8644,19 @@
       </c>
       <c r="B30" s="1" cm="1">
         <f t="array" aca="1" ref="B30:E30" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C30" s="1">
         <f ca="1"/>
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="D30" s="1">
         <f ca="1"/>
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="E30" s="1">
         <f ca="1"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="N30" s="1">
         <v>40001</v>
@@ -8890,19 +8890,19 @@
       </c>
       <c r="B31" s="1" cm="1">
         <f t="array" aca="1" ref="B31:E31" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C31" s="1">
         <f ca="1"/>
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D31" s="1">
         <f ca="1"/>
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="E31" s="1">
         <f ca="1"/>
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="N31" s="1">
         <v>40001</v>
@@ -9136,19 +9136,19 @@
       </c>
       <c r="B32" s="1" cm="1">
         <f t="array" aca="1" ref="B32:E32" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C32" s="1">
         <f ca="1"/>
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D32" s="1">
         <f ca="1"/>
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E32" s="1">
         <f ca="1"/>
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="N32" s="1">
         <v>40001</v>
@@ -9382,19 +9382,19 @@
       </c>
       <c r="B33" s="1" cm="1">
         <f t="array" aca="1" ref="B33:E33" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C33" s="1">
         <f ca="1"/>
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D33" s="1">
         <f ca="1"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E33" s="1">
         <f ca="1"/>
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="N33" s="1">
         <v>40001</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_shop_equip_list_v8【迷宫-商店购买装备队列】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_shop_equip_list_v8【迷宫-商店购买装备队列】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C091EB-7432-4719-9DD5-B48B19A7EFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7FC3927-71A6-4E87-B798-79D343BFDAD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B965FE27-C998-4B23-9CF9-52FD9DD9A018}"/>
   </bookViews>
@@ -312,7 +312,7 @@
     <t>42618001,42633001,42614001,42657001,42636001,42615001,42618001,42634001,42617001,42656001,42612001,42615001,42638001,42614001,42617001,42731001,42612001,42658001,42616001,42617001,42731001,42612001,42633001,42616001</t>
   </si>
   <si>
-    <t>42633001,42617001,42616001,42618001,42632001,42615001</t>
+    <t>42633001,42617001,42616001,42618001,42652001,42635001</t>
   </si>
 </sst>
 </file>
@@ -1667,19 +1667,19 @@
       </c>
       <c r="B3" s="1" cm="1">
         <f t="array" aca="1" ref="B3:E3" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C3" s="1">
         <f ca="1"/>
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1">
         <f ca="1"/>
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="E3" s="1">
         <f ca="1"/>
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="G3" s="1">
         <v>100</v>
@@ -1928,19 +1928,19 @@
       </c>
       <c r="B4" s="1" cm="1">
         <f t="array" aca="1" ref="B4:E4" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1">
         <f ca="1"/>
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D4" s="1">
         <f ca="1"/>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1">
         <f ca="1"/>
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
         <f>G3+1</f>
@@ -2190,19 +2190,19 @@
       </c>
       <c r="B5" s="1" cm="1">
         <f t="array" aca="1" ref="B5:E5" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C5" s="1">
         <f ca="1"/>
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D5" s="1">
         <f ca="1"/>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E5" s="1">
         <f ca="1"/>
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="G5" s="1">
         <f>G4+1</f>
@@ -2452,19 +2452,19 @@
       </c>
       <c r="B6" s="1" cm="1">
         <f t="array" aca="1" ref="B6:E6" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1">
         <f ca="1"/>
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D6" s="1">
         <f ca="1"/>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E6" s="1">
         <f ca="1"/>
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1">
         <f>G5+1</f>
@@ -2714,19 +2714,19 @@
       </c>
       <c r="B7" s="1" cm="1">
         <f t="array" aca="1" ref="B7:E7" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C7" s="1">
         <f ca="1"/>
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D7" s="1">
         <f ca="1"/>
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="E7" s="1">
         <f ca="1"/>
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G7" s="1">
         <f>G6+1</f>
@@ -2977,19 +2977,19 @@
       </c>
       <c r="B8" s="1" cm="1">
         <f t="array" aca="1" ref="B8:E8" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C8" s="1">
         <f ca="1"/>
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1">
         <f ca="1"/>
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E8" s="1">
         <f ca="1"/>
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" ref="G8:G22" si="4">G3+100</f>
@@ -3240,19 +3240,19 @@
       </c>
       <c r="B9" s="1" cm="1">
         <f t="array" aca="1" ref="B9:E9" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="C9" s="1">
         <f ca="1"/>
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D9" s="1">
         <f ca="1"/>
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E9" s="1">
         <f ca="1"/>
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G9" s="1">
         <f t="shared" si="4"/>
@@ -3503,19 +3503,19 @@
       </c>
       <c r="B10" s="1" cm="1">
         <f t="array" aca="1" ref="B10:E10" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C10" s="1">
         <f ca="1"/>
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1">
         <f ca="1"/>
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E10" s="1">
         <f ca="1"/>
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" si="4"/>
@@ -3766,19 +3766,19 @@
       </c>
       <c r="B11" s="1" cm="1">
         <f t="array" aca="1" ref="B11:E11" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <f ca="1"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1">
         <f ca="1"/>
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="E11" s="1">
         <f ca="1"/>
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" si="4"/>
@@ -4029,19 +4029,19 @@
       </c>
       <c r="B12" s="1" cm="1">
         <f t="array" aca="1" ref="B12:E12" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C12" s="1">
         <f ca="1"/>
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D12" s="1">
         <f ca="1"/>
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1">
         <f ca="1"/>
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="4"/>
@@ -4292,19 +4292,19 @@
       </c>
       <c r="B13" s="1" cm="1">
         <f t="array" aca="1" ref="B13:E13" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C13" s="1">
         <f ca="1"/>
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D13" s="1">
         <f ca="1"/>
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="E13" s="1">
         <f ca="1"/>
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="G13" s="1">
         <f t="shared" si="4"/>
@@ -4555,19 +4555,19 @@
       </c>
       <c r="B14" s="1" cm="1">
         <f t="array" aca="1" ref="B14:E14" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C14" s="1">
         <f ca="1"/>
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D14" s="1">
         <f ca="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" s="1">
         <f ca="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G14" s="1">
         <f t="shared" si="4"/>
@@ -4818,19 +4818,19 @@
       </c>
       <c r="B15" s="1" cm="1">
         <f t="array" aca="1" ref="B15:E15" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1">
         <f ca="1"/>
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="D15" s="1">
         <f ca="1"/>
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E15" s="1">
         <f ca="1"/>
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" si="4"/>
@@ -5081,19 +5081,19 @@
       </c>
       <c r="B16" s="1" cm="1">
         <f t="array" aca="1" ref="B16:E16" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C16" s="1">
         <f ca="1"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D16" s="1">
         <f ca="1"/>
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="E16" s="1">
         <f ca="1"/>
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="G16" s="1">
         <f t="shared" si="4"/>
@@ -5344,19 +5344,19 @@
       </c>
       <c r="B17" s="1" cm="1">
         <f t="array" aca="1" ref="B17:E17" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1">
         <f ca="1"/>
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D17" s="1">
         <f ca="1"/>
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E17" s="1">
         <f ca="1"/>
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" si="4"/>
@@ -5607,19 +5607,19 @@
       </c>
       <c r="B18" s="1" cm="1">
         <f t="array" aca="1" ref="B18:E18" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C18" s="1">
         <f ca="1"/>
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D18" s="1">
         <f ca="1"/>
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E18" s="1">
         <f ca="1"/>
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" si="4"/>
@@ -5870,19 +5870,19 @@
       </c>
       <c r="B19" s="1" cm="1">
         <f t="array" aca="1" ref="B19:E19" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C19" s="1">
         <f ca="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D19" s="1">
         <f ca="1"/>
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="E19" s="1">
         <f ca="1"/>
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" si="4"/>
@@ -6133,19 +6133,19 @@
       </c>
       <c r="B20" s="1" cm="1">
         <f t="array" aca="1" ref="B20:E20" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C20" s="1">
         <f ca="1"/>
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="D20" s="1">
         <f ca="1"/>
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="E20" s="1">
         <f ca="1"/>
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" si="4"/>
@@ -6396,15 +6396,15 @@
       </c>
       <c r="B21" s="1" cm="1">
         <f t="array" aca="1" ref="B21:E21" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C21" s="1">
         <f ca="1"/>
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D21" s="1">
         <f ca="1"/>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E21" s="1">
         <f ca="1"/>
@@ -6659,19 +6659,19 @@
       </c>
       <c r="B22" s="1" cm="1">
         <f t="array" aca="1" ref="B22:E22" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C22" s="1">
         <f ca="1"/>
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="D22" s="1">
         <f ca="1"/>
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E22" s="1">
         <f ca="1"/>
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G22" s="1">
         <f t="shared" si="4"/>
@@ -6922,19 +6922,19 @@
       </c>
       <c r="B23" s="1" cm="1">
         <f t="array" aca="1" ref="B23:E23" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C23" s="1">
         <f ca="1"/>
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D23" s="1">
         <f ca="1"/>
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E23" s="1">
         <f ca="1"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N23" s="1">
         <v>40001</v>
@@ -7168,19 +7168,19 @@
       </c>
       <c r="B24" s="1" cm="1">
         <f t="array" aca="1" ref="B24:E24" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C24" s="1">
         <f ca="1"/>
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="D24" s="1">
         <f ca="1"/>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E24" s="1">
         <f ca="1"/>
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="N24" s="1">
         <v>40001</v>
@@ -7418,15 +7418,15 @@
       </c>
       <c r="C25" s="1">
         <f ca="1"/>
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D25" s="1">
         <f ca="1"/>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E25" s="1">
         <f ca="1"/>
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="N25" s="1">
         <v>40001</v>
@@ -7660,19 +7660,19 @@
       </c>
       <c r="B26" s="1" cm="1">
         <f t="array" aca="1" ref="B26:E26" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C26" s="1">
         <f ca="1"/>
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D26" s="1">
         <f ca="1"/>
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E26" s="1">
         <f ca="1"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N26" s="1">
         <v>40001</v>
@@ -7906,19 +7906,19 @@
       </c>
       <c r="B27" s="1" cm="1">
         <f t="array" aca="1" ref="B27:E27" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C27" s="1">
         <f ca="1"/>
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D27" s="1">
         <f ca="1"/>
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E27" s="1">
         <f ca="1"/>
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="N27" s="1">
         <v>40001</v>
@@ -8152,19 +8152,19 @@
       </c>
       <c r="B28" s="1" cm="1">
         <f t="array" aca="1" ref="B28:E28" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="C28" s="1">
         <f ca="1"/>
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D28" s="1">
         <f ca="1"/>
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E28" s="1">
         <f ca="1"/>
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="N28" s="1">
         <v>40001</v>
@@ -8398,19 +8398,19 @@
       </c>
       <c r="B29" s="1" cm="1">
         <f t="array" aca="1" ref="B29:E29" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C29" s="1">
         <f ca="1"/>
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D29" s="1">
         <f ca="1"/>
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="E29" s="1">
         <f ca="1"/>
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="N29" s="1">
         <v>40001</v>
@@ -8644,19 +8644,19 @@
       </c>
       <c r="B30" s="1" cm="1">
         <f t="array" aca="1" ref="B30:E30" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C30" s="1">
         <f ca="1"/>
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D30" s="1">
         <f ca="1"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E30" s="1">
         <f ca="1"/>
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="N30" s="1">
         <v>40001</v>
@@ -8890,19 +8890,19 @@
       </c>
       <c r="B31" s="1" cm="1">
         <f t="array" aca="1" ref="B31:E31" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C31" s="1">
         <f ca="1"/>
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="D31" s="1">
         <f ca="1"/>
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="E31" s="1">
         <f ca="1"/>
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="N31" s="1">
         <v>40001</v>
@@ -9136,19 +9136,19 @@
       </c>
       <c r="B32" s="1" cm="1">
         <f t="array" aca="1" ref="B32:E32" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C32" s="1">
         <f ca="1"/>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D32" s="1">
         <f ca="1"/>
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="E32" s="1">
         <f ca="1"/>
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="N32" s="1">
         <v>40001</v>
@@ -9382,19 +9382,19 @@
       </c>
       <c r="B33" s="1" cm="1">
         <f t="array" aca="1" ref="B33:E33" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C33" s="1">
         <f ca="1"/>
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D33" s="1">
         <f ca="1"/>
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E33" s="1">
         <f ca="1"/>
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="N33" s="1">
         <v>40001</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_shop_equip_list_v8【迷宫-商店购买装备队列】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_shop_equip_list_v8【迷宫-商店购买装备队列】.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7FC3927-71A6-4E87-B798-79D343BFDAD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4AD55E-59ED-494C-B9FD-25349361B594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B965FE27-C998-4B23-9CF9-52FD9DD9A018}"/>
   </bookViews>
@@ -312,7 +312,7 @@
     <t>42618001,42633001,42614001,42657001,42636001,42615001,42618001,42634001,42617001,42656001,42612001,42615001,42638001,42614001,42617001,42731001,42612001,42658001,42616001,42617001,42731001,42612001,42633001,42616001</t>
   </si>
   <si>
-    <t>42633001,42617001,42616001,42618001,42652001,42635001</t>
+    <t>42617001,42615001,42633001,42616001,42638001,42612001,42614001,42636001,42617001,42618001,42751001,42613001,42637001,42634001,42653001,42615001</t>
   </si>
 </sst>
 </file>
@@ -1667,19 +1667,19 @@
       </c>
       <c r="B3" s="1" cm="1">
         <f t="array" aca="1" ref="B3:E3" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1">
         <f ca="1"/>
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D3" s="1">
         <f ca="1"/>
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E3" s="1">
         <f ca="1"/>
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1">
         <v>100</v>
@@ -1928,19 +1928,19 @@
       </c>
       <c r="B4" s="1" cm="1">
         <f t="array" aca="1" ref="B4:E4" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <f ca="1"/>
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="D4" s="1">
         <f ca="1"/>
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E4" s="1">
         <f ca="1"/>
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="G4" s="1">
         <f>G3+1</f>
@@ -2190,19 +2190,19 @@
       </c>
       <c r="B5" s="1" cm="1">
         <f t="array" aca="1" ref="B5:E5" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1">
         <f ca="1"/>
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1">
         <f ca="1"/>
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="E5" s="1">
         <f ca="1"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" s="1">
         <f>G4+1</f>
@@ -2452,19 +2452,19 @@
       </c>
       <c r="B6" s="1" cm="1">
         <f t="array" aca="1" ref="B6:E6" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="C6" s="1">
         <f ca="1"/>
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1">
         <f ca="1"/>
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="E6" s="1">
         <f ca="1"/>
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="G6" s="1">
         <f>G5+1</f>
@@ -2714,19 +2714,19 @@
       </c>
       <c r="B7" s="1" cm="1">
         <f t="array" aca="1" ref="B7:E7" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C7" s="1">
         <f ca="1"/>
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D7" s="1">
         <f ca="1"/>
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="E7" s="1">
         <f ca="1"/>
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G7" s="1">
         <f>G6+1</f>
@@ -2977,19 +2977,19 @@
       </c>
       <c r="B8" s="1" cm="1">
         <f t="array" aca="1" ref="B8:E8" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1">
         <f ca="1"/>
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D8" s="1">
         <f ca="1"/>
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E8" s="1">
         <f ca="1"/>
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" ref="G8:G22" si="4">G3+100</f>
@@ -3240,19 +3240,19 @@
       </c>
       <c r="B9" s="1" cm="1">
         <f t="array" aca="1" ref="B9:E9" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1">
         <f ca="1"/>
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D9" s="1">
         <f ca="1"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E9" s="1">
         <f ca="1"/>
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="G9" s="1">
         <f t="shared" si="4"/>
@@ -3503,15 +3503,15 @@
       </c>
       <c r="B10" s="1" cm="1">
         <f t="array" aca="1" ref="B10:E10" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C10" s="1">
         <f ca="1"/>
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="D10" s="1">
         <f ca="1"/>
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E10" s="1">
         <f ca="1"/>
@@ -3766,19 +3766,19 @@
       </c>
       <c r="B11" s="1" cm="1">
         <f t="array" aca="1" ref="B11:E11" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" s="1">
         <f ca="1"/>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D11" s="1">
         <f ca="1"/>
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="E11" s="1">
         <f ca="1"/>
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" si="4"/>
@@ -4029,19 +4029,19 @@
       </c>
       <c r="B12" s="1" cm="1">
         <f t="array" aca="1" ref="B12:E12" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C12" s="1">
         <f ca="1"/>
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D12" s="1">
         <f ca="1"/>
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="E12" s="1">
         <f ca="1"/>
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="4"/>
@@ -4292,11 +4292,11 @@
       </c>
       <c r="B13" s="1" cm="1">
         <f t="array" aca="1" ref="B13:E13" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C13" s="1">
         <f ca="1"/>
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="D13" s="1">
         <f ca="1"/>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="E13" s="1">
         <f ca="1"/>
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="G13" s="1">
         <f t="shared" si="4"/>
@@ -4555,19 +4555,19 @@
       </c>
       <c r="B14" s="1" cm="1">
         <f t="array" aca="1" ref="B14:E14" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C14" s="1">
         <f ca="1"/>
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D14" s="1">
         <f ca="1"/>
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="E14" s="1">
         <f ca="1"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G14" s="1">
         <f t="shared" si="4"/>
@@ -4818,15 +4818,15 @@
       </c>
       <c r="B15" s="1" cm="1">
         <f t="array" aca="1" ref="B15:E15" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="C15" s="1">
         <f ca="1"/>
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="D15" s="1">
         <f ca="1"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E15" s="1">
         <f ca="1"/>
@@ -5081,19 +5081,19 @@
       </c>
       <c r="B16" s="1" cm="1">
         <f t="array" aca="1" ref="B16:E16" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" s="1">
         <f ca="1"/>
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D16" s="1">
         <f ca="1"/>
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E16" s="1">
         <f ca="1"/>
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G16" s="1">
         <f t="shared" si="4"/>
@@ -5344,19 +5344,19 @@
       </c>
       <c r="B17" s="1" cm="1">
         <f t="array" aca="1" ref="B17:E17" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C17" s="1">
         <f ca="1"/>
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D17" s="1">
         <f ca="1"/>
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="E17" s="1">
         <f ca="1"/>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" si="4"/>
@@ -5607,19 +5607,19 @@
       </c>
       <c r="B18" s="1" cm="1">
         <f t="array" aca="1" ref="B18:E18" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C18" s="1">
         <f ca="1"/>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" s="1">
         <f ca="1"/>
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="E18" s="1">
         <f ca="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" si="4"/>
@@ -5870,19 +5870,19 @@
       </c>
       <c r="B19" s="1" cm="1">
         <f t="array" aca="1" ref="B19:E19" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C19" s="1">
         <f ca="1"/>
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="D19" s="1">
         <f ca="1"/>
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E19" s="1">
         <f ca="1"/>
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" si="4"/>
@@ -6133,19 +6133,19 @@
       </c>
       <c r="B20" s="1" cm="1">
         <f t="array" aca="1" ref="B20:E20" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C20" s="1">
         <f ca="1"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D20" s="1">
         <f ca="1"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E20" s="1">
         <f ca="1"/>
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" si="4"/>
@@ -6396,19 +6396,19 @@
       </c>
       <c r="B21" s="1" cm="1">
         <f t="array" aca="1" ref="B21:E21" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C21" s="1">
         <f ca="1"/>
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D21" s="1">
         <f ca="1"/>
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="E21" s="1">
         <f ca="1"/>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G21" s="1">
         <f t="shared" si="4"/>
@@ -6659,19 +6659,19 @@
       </c>
       <c r="B22" s="1" cm="1">
         <f t="array" aca="1" ref="B22:E22" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C22" s="1">
         <f ca="1"/>
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="D22" s="1">
         <f ca="1"/>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E22" s="1">
         <f ca="1"/>
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G22" s="1">
         <f t="shared" si="4"/>
@@ -6922,19 +6922,19 @@
       </c>
       <c r="B23" s="1" cm="1">
         <f t="array" aca="1" ref="B23:E23" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C23" s="1">
         <f ca="1"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D23" s="1">
         <f ca="1"/>
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E23" s="1">
         <f ca="1"/>
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="N23" s="1">
         <v>40001</v>
@@ -7168,19 +7168,19 @@
       </c>
       <c r="B24" s="1" cm="1">
         <f t="array" aca="1" ref="B24:E24" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C24" s="1">
         <f ca="1"/>
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D24" s="1">
         <f ca="1"/>
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E24" s="1">
         <f ca="1"/>
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="N24" s="1">
         <v>40001</v>
@@ -7414,19 +7414,19 @@
       </c>
       <c r="B25" s="1" cm="1">
         <f t="array" aca="1" ref="B25:E25" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C25" s="1">
         <f ca="1"/>
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="D25" s="1">
         <f ca="1"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E25" s="1">
         <f ca="1"/>
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="N25" s="1">
         <v>40001</v>
@@ -7660,19 +7660,19 @@
       </c>
       <c r="B26" s="1" cm="1">
         <f t="array" aca="1" ref="B26:E26" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C26" s="1">
         <f ca="1"/>
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D26" s="1">
         <f ca="1"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E26" s="1">
         <f ca="1"/>
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="N26" s="1">
         <v>40001</v>
@@ -7906,19 +7906,19 @@
       </c>
       <c r="B27" s="1" cm="1">
         <f t="array" aca="1" ref="B27:E27" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="C27" s="1">
         <f ca="1"/>
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D27" s="1">
         <f ca="1"/>
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E27" s="1">
         <f ca="1"/>
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="N27" s="1">
         <v>40001</v>
@@ -8152,19 +8152,19 @@
       </c>
       <c r="B28" s="1" cm="1">
         <f t="array" aca="1" ref="B28:E28" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C28" s="1">
         <f ca="1"/>
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D28" s="1">
         <f ca="1"/>
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E28" s="1">
         <f ca="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N28" s="1">
         <v>40001</v>
@@ -8398,19 +8398,19 @@
       </c>
       <c r="B29" s="1" cm="1">
         <f t="array" aca="1" ref="B29:E29" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C29" s="1">
         <f ca="1"/>
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D29" s="1">
         <f ca="1"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E29" s="1">
         <f ca="1"/>
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="N29" s="1">
         <v>40001</v>
@@ -8644,19 +8644,19 @@
       </c>
       <c r="B30" s="1" cm="1">
         <f t="array" aca="1" ref="B30:E30" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="C30" s="1">
         <f ca="1"/>
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="D30" s="1">
         <f ca="1"/>
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="E30" s="1">
         <f ca="1"/>
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="N30" s="1">
         <v>40001</v>
@@ -8890,19 +8890,19 @@
       </c>
       <c r="B31" s="1" cm="1">
         <f t="array" aca="1" ref="B31:E31" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="C31" s="1">
         <f ca="1"/>
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="D31" s="1">
         <f ca="1"/>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E31" s="1">
         <f ca="1"/>
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="N31" s="1">
         <v>40001</v>
@@ -9136,19 +9136,19 @@
       </c>
       <c r="B32" s="1" cm="1">
         <f t="array" aca="1" ref="B32:E32" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C32" s="1">
         <f ca="1"/>
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D32" s="1">
         <f ca="1"/>
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E32" s="1">
         <f ca="1"/>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="N32" s="1">
         <v>40001</v>
@@ -9382,19 +9382,19 @@
       </c>
       <c r="B33" s="1" cm="1">
         <f t="array" aca="1" ref="B33:E33" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="C33" s="1">
         <f ca="1"/>
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D33" s="1">
         <f ca="1"/>
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="E33" s="1">
         <f ca="1"/>
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N33" s="1">
         <v>40001</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_shop_equip_list_v8【迷宫-商店购买装备队列】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_shop_equip_list_v8【迷宫-商店购买装备队列】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4AD55E-59ED-494C-B9FD-25349361B594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D717A22D-8145-4A09-BC94-EEECBE447846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B965FE27-C998-4B23-9CF9-52FD9DD9A018}"/>
   </bookViews>
@@ -312,7 +312,7 @@
     <t>42618001,42633001,42614001,42657001,42636001,42615001,42618001,42634001,42617001,42656001,42612001,42615001,42638001,42614001,42617001,42731001,42612001,42658001,42616001,42617001,42731001,42612001,42633001,42616001</t>
   </si>
   <si>
-    <t>42617001,42615001,42633001,42616001,42638001,42612001,42614001,42636001,42617001,42618001,42751001,42613001,42637001,42634001,42653001,42615001</t>
+    <t>42615001,42616001,42632001,42613001,42637001,42711001,42634001,42618001,42613001,42634001,42616001,42751001,42633001,42615001,42638001,42614001,42657001,42632001,42731001,42614001,42653001,42637001,42618001,42616001,42655001,42632001,42731001,42636001</t>
   </si>
 </sst>
 </file>
@@ -1667,19 +1667,19 @@
       </c>
       <c r="B3" s="1" cm="1">
         <f t="array" aca="1" ref="B3:E3" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
         <f ca="1"/>
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1">
         <f ca="1"/>
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1">
         <f ca="1"/>
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="G3" s="1">
         <v>100</v>
@@ -1928,19 +1928,19 @@
       </c>
       <c r="B4" s="1" cm="1">
         <f t="array" aca="1" ref="B4:E4" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1">
         <f ca="1"/>
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="D4" s="1">
         <f ca="1"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" s="1">
         <f ca="1"/>
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1">
         <f>G3+1</f>
@@ -2190,19 +2190,19 @@
       </c>
       <c r="B5" s="1" cm="1">
         <f t="array" aca="1" ref="B5:E5" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C5" s="1">
         <f ca="1"/>
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="D5" s="1">
         <f ca="1"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5" s="1">
         <f ca="1"/>
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
         <f>G4+1</f>
@@ -2452,19 +2452,19 @@
       </c>
       <c r="B6" s="1" cm="1">
         <f t="array" aca="1" ref="B6:E6" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C6" s="1">
         <f ca="1"/>
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D6" s="1">
         <f ca="1"/>
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="E6" s="1">
         <f ca="1"/>
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
         <f>G5+1</f>
@@ -2714,19 +2714,19 @@
       </c>
       <c r="B7" s="1" cm="1">
         <f t="array" aca="1" ref="B7:E7" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C7" s="1">
         <f ca="1"/>
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D7" s="1">
         <f ca="1"/>
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E7" s="1">
         <f ca="1"/>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G7" s="1">
         <f>G6+1</f>
@@ -2977,19 +2977,19 @@
       </c>
       <c r="B8" s="1" cm="1">
         <f t="array" aca="1" ref="B8:E8" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <f ca="1"/>
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D8" s="1">
         <f ca="1"/>
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E8" s="1">
         <f ca="1"/>
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" ref="G8:G22" si="4">G3+100</f>
@@ -3240,19 +3240,19 @@
       </c>
       <c r="B9" s="1" cm="1">
         <f t="array" aca="1" ref="B9:E9" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C9" s="1">
         <f ca="1"/>
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1">
         <f ca="1"/>
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E9" s="1">
         <f ca="1"/>
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="G9" s="1">
         <f t="shared" si="4"/>
@@ -3503,19 +3503,19 @@
       </c>
       <c r="B10" s="1" cm="1">
         <f t="array" aca="1" ref="B10:E10" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1">
         <f ca="1"/>
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D10" s="1">
         <f ca="1"/>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E10" s="1">
         <f ca="1"/>
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" si="4"/>
@@ -3766,19 +3766,19 @@
       </c>
       <c r="B11" s="1" cm="1">
         <f t="array" aca="1" ref="B11:E11" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C11" s="1">
         <f ca="1"/>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D11" s="1">
         <f ca="1"/>
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E11" s="1">
         <f ca="1"/>
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" si="4"/>
@@ -4029,19 +4029,19 @@
       </c>
       <c r="B12" s="1" cm="1">
         <f t="array" aca="1" ref="B12:E12" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C12" s="1">
         <f ca="1"/>
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="D12" s="1">
         <f ca="1"/>
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="E12" s="1">
         <f ca="1"/>
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="4"/>
@@ -4292,19 +4292,19 @@
       </c>
       <c r="B13" s="1" cm="1">
         <f t="array" aca="1" ref="B13:E13" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C13" s="1">
         <f ca="1"/>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D13" s="1">
         <f ca="1"/>
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="E13" s="1">
         <f ca="1"/>
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G13" s="1">
         <f t="shared" si="4"/>
@@ -4555,19 +4555,19 @@
       </c>
       <c r="B14" s="1" cm="1">
         <f t="array" aca="1" ref="B14:E14" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C14" s="1">
         <f ca="1"/>
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="D14" s="1">
         <f ca="1"/>
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E14" s="1">
         <f ca="1"/>
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G14" s="1">
         <f t="shared" si="4"/>
@@ -4818,19 +4818,19 @@
       </c>
       <c r="B15" s="1" cm="1">
         <f t="array" aca="1" ref="B15:E15" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="C15" s="1">
         <f ca="1"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D15" s="1">
         <f ca="1"/>
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="E15" s="1">
         <f ca="1"/>
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" si="4"/>
@@ -5081,19 +5081,19 @@
       </c>
       <c r="B16" s="1" cm="1">
         <f t="array" aca="1" ref="B16:E16" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1">
         <f ca="1"/>
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D16" s="1">
         <f ca="1"/>
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E16" s="1">
         <f ca="1"/>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G16" s="1">
         <f t="shared" si="4"/>
@@ -5344,19 +5344,19 @@
       </c>
       <c r="B17" s="1" cm="1">
         <f t="array" aca="1" ref="B17:E17" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C17" s="1">
         <f ca="1"/>
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D17" s="1">
         <f ca="1"/>
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="E17" s="1">
         <f ca="1"/>
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" si="4"/>
@@ -5607,19 +5607,19 @@
       </c>
       <c r="B18" s="1" cm="1">
         <f t="array" aca="1" ref="B18:E18" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="C18" s="1">
         <f ca="1"/>
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D18" s="1">
         <f ca="1"/>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E18" s="1">
         <f ca="1"/>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" si="4"/>
@@ -5870,19 +5870,19 @@
       </c>
       <c r="B19" s="1" cm="1">
         <f t="array" aca="1" ref="B19:E19" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C19" s="1">
         <f ca="1"/>
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D19" s="1">
         <f ca="1"/>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E19" s="1">
         <f ca="1"/>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" si="4"/>
@@ -6133,19 +6133,19 @@
       </c>
       <c r="B20" s="1" cm="1">
         <f t="array" aca="1" ref="B20:E20" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C20" s="1">
         <f ca="1"/>
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D20" s="1">
         <f ca="1"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E20" s="1">
         <f ca="1"/>
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" si="4"/>
@@ -6396,19 +6396,19 @@
       </c>
       <c r="B21" s="1" cm="1">
         <f t="array" aca="1" ref="B21:E21" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C21" s="1">
         <f ca="1"/>
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D21" s="1">
         <f ca="1"/>
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1">
         <f ca="1"/>
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G21" s="1">
         <f t="shared" si="4"/>
@@ -6659,19 +6659,19 @@
       </c>
       <c r="B22" s="1" cm="1">
         <f t="array" aca="1" ref="B22:E22" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C22" s="1">
         <f ca="1"/>
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D22" s="1">
         <f ca="1"/>
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E22" s="1">
         <f ca="1"/>
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="G22" s="1">
         <f t="shared" si="4"/>
@@ -6922,19 +6922,19 @@
       </c>
       <c r="B23" s="1" cm="1">
         <f t="array" aca="1" ref="B23:E23" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C23" s="1">
         <f ca="1"/>
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D23" s="1">
         <f ca="1"/>
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E23" s="1">
         <f ca="1"/>
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="N23" s="1">
         <v>40001</v>
@@ -7168,19 +7168,19 @@
       </c>
       <c r="B24" s="1" cm="1">
         <f t="array" aca="1" ref="B24:E24" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C24" s="1">
         <f ca="1"/>
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="D24" s="1">
         <f ca="1"/>
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E24" s="1">
         <f ca="1"/>
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N24" s="1">
         <v>40001</v>
@@ -7414,19 +7414,19 @@
       </c>
       <c r="B25" s="1" cm="1">
         <f t="array" aca="1" ref="B25:E25" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C25" s="1">
         <f ca="1"/>
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D25" s="1">
         <f ca="1"/>
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="E25" s="1">
         <f ca="1"/>
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="N25" s="1">
         <v>40001</v>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="B26" s="1" cm="1">
         <f t="array" aca="1" ref="B26:E26" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C26" s="1">
         <f ca="1"/>
@@ -7668,11 +7668,11 @@
       </c>
       <c r="D26" s="1">
         <f ca="1"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E26" s="1">
         <f ca="1"/>
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="N26" s="1">
         <v>40001</v>
@@ -7906,19 +7906,19 @@
       </c>
       <c r="B27" s="1" cm="1">
         <f t="array" aca="1" ref="B27:E27" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="C27" s="1">
         <f ca="1"/>
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D27" s="1">
         <f ca="1"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E27" s="1">
         <f ca="1"/>
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="N27" s="1">
         <v>40001</v>
@@ -8152,19 +8152,19 @@
       </c>
       <c r="B28" s="1" cm="1">
         <f t="array" aca="1" ref="B28:E28" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C28" s="1">
         <f ca="1"/>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D28" s="1">
         <f ca="1"/>
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="E28" s="1">
         <f ca="1"/>
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="N28" s="1">
         <v>40001</v>
@@ -8398,19 +8398,19 @@
       </c>
       <c r="B29" s="1" cm="1">
         <f t="array" aca="1" ref="B29:E29" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="C29" s="1">
         <f ca="1"/>
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="D29" s="1">
         <f ca="1"/>
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E29" s="1">
         <f ca="1"/>
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="N29" s="1">
         <v>40001</v>
@@ -8644,19 +8644,19 @@
       </c>
       <c r="B30" s="1" cm="1">
         <f t="array" aca="1" ref="B30:E30" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C30" s="1">
         <f ca="1"/>
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="D30" s="1">
         <f ca="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E30" s="1">
         <f ca="1"/>
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="N30" s="1">
         <v>40001</v>
@@ -8890,11 +8890,11 @@
       </c>
       <c r="B31" s="1" cm="1">
         <f t="array" aca="1" ref="B31:E31" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="C31" s="1">
         <f ca="1"/>
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D31" s="1">
         <f ca="1"/>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="E31" s="1">
         <f ca="1"/>
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="N31" s="1">
         <v>40001</v>
@@ -9136,19 +9136,19 @@
       </c>
       <c r="B32" s="1" cm="1">
         <f t="array" aca="1" ref="B32:E32" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="C32" s="1">
         <f ca="1"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D32" s="1">
         <f ca="1"/>
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="E32" s="1">
         <f ca="1"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="N32" s="1">
         <v>40001</v>
@@ -9382,19 +9382,19 @@
       </c>
       <c r="B33" s="1" cm="1">
         <f t="array" aca="1" ref="B33:E33" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C33" s="1">
         <f ca="1"/>
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="D33" s="1">
         <f ca="1"/>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E33" s="1">
         <f ca="1"/>
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="N33" s="1">
         <v>40001</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_shop_equip_list_v8【迷宫-商店购买装备队列】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_shop_equip_list_v8【迷宫-商店购买装备队列】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D717A22D-8145-4A09-BC94-EEECBE447846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A8B7F2-0A9A-4DFC-AE5D-829EDB328990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B965FE27-C998-4B23-9CF9-52FD9DD9A018}"/>
   </bookViews>
@@ -312,7 +312,7 @@
     <t>42618001,42633001,42614001,42657001,42636001,42615001,42618001,42634001,42617001,42656001,42612001,42615001,42638001,42614001,42617001,42731001,42612001,42658001,42616001,42617001,42731001,42612001,42633001,42616001</t>
   </si>
   <si>
-    <t>42615001,42616001,42632001,42613001,42637001,42711001,42634001,42618001,42613001,42634001,42616001,42751001,42633001,42615001,42638001,42614001,42657001,42632001,42731001,42614001,42653001,42637001,42618001,42616001,42655001,42632001,42731001,42636001</t>
+    <t>42615001,42616001,42632001,42613001,42711001,42634001,42618001,42616001,42751001,42633001,42615001,42638001,42614001,42657001,42731001,42633001,42616001,42655001,42632001,42731001,42636001,42652001,42636001,42638001,42731001</t>
   </si>
 </sst>
 </file>
@@ -1667,19 +1667,19 @@
       </c>
       <c r="B3" s="1" cm="1">
         <f t="array" aca="1" ref="B3:E3" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C3" s="1">
         <f ca="1"/>
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1">
         <f ca="1"/>
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E3" s="1">
         <f ca="1"/>
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1">
         <v>100</v>
@@ -1928,19 +1928,19 @@
       </c>
       <c r="B4" s="1" cm="1">
         <f t="array" aca="1" ref="B4:E4" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1">
         <f ca="1"/>
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1">
         <f ca="1"/>
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E4" s="1">
         <f ca="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" s="1">
         <f>G3+1</f>
@@ -2190,19 +2190,19 @@
       </c>
       <c r="B5" s="1" cm="1">
         <f t="array" aca="1" ref="B5:E5" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1">
         <f ca="1"/>
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1">
         <f ca="1"/>
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="E5" s="1">
         <f ca="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
         <f>G4+1</f>
@@ -2452,19 +2452,19 @@
       </c>
       <c r="B6" s="1" cm="1">
         <f t="array" aca="1" ref="B6:E6" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1">
         <f ca="1"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D6" s="1">
         <f ca="1"/>
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="E6" s="1">
         <f ca="1"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
         <f>G5+1</f>
@@ -2714,19 +2714,19 @@
       </c>
       <c r="B7" s="1" cm="1">
         <f t="array" aca="1" ref="B7:E7" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1">
         <f ca="1"/>
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1">
         <f ca="1"/>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E7" s="1">
         <f ca="1"/>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G7" s="1">
         <f>G6+1</f>
@@ -2977,19 +2977,19 @@
       </c>
       <c r="B8" s="1" cm="1">
         <f t="array" aca="1" ref="B8:E8" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C8" s="1">
         <f ca="1"/>
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="D8" s="1">
         <f ca="1"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1">
         <f ca="1"/>
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" ref="G8:G22" si="4">G3+100</f>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="B9" s="1" cm="1">
         <f t="array" aca="1" ref="B9:E9" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C9" s="1">
         <f ca="1"/>
@@ -3248,11 +3248,11 @@
       </c>
       <c r="D9" s="1">
         <f ca="1"/>
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E9" s="1">
         <f ca="1"/>
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G9" s="1">
         <f t="shared" si="4"/>
@@ -3503,19 +3503,19 @@
       </c>
       <c r="B10" s="1" cm="1">
         <f t="array" aca="1" ref="B10:E10" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C10" s="1">
         <f ca="1"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D10" s="1">
         <f ca="1"/>
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="E10" s="1">
         <f ca="1"/>
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" si="4"/>
@@ -3766,19 +3766,19 @@
       </c>
       <c r="B11" s="1" cm="1">
         <f t="array" aca="1" ref="B11:E11" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C11" s="1">
         <f ca="1"/>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D11" s="1">
         <f ca="1"/>
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E11" s="1">
         <f ca="1"/>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" si="4"/>
@@ -4029,19 +4029,19 @@
       </c>
       <c r="B12" s="1" cm="1">
         <f t="array" aca="1" ref="B12:E12" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C12" s="1">
         <f ca="1"/>
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D12" s="1">
         <f ca="1"/>
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="E12" s="1">
         <f ca="1"/>
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="4"/>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="B13" s="1" cm="1">
         <f t="array" aca="1" ref="B13:E13" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C13" s="1">
         <f ca="1"/>
@@ -4300,11 +4300,11 @@
       </c>
       <c r="D13" s="1">
         <f ca="1"/>
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E13" s="1">
         <f ca="1"/>
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G13" s="1">
         <f t="shared" si="4"/>
@@ -4555,19 +4555,19 @@
       </c>
       <c r="B14" s="1" cm="1">
         <f t="array" aca="1" ref="B14:E14" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C14" s="1">
         <f ca="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14" s="1">
         <f ca="1"/>
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E14" s="1">
         <f ca="1"/>
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="G14" s="1">
         <f t="shared" si="4"/>
@@ -4818,19 +4818,19 @@
       </c>
       <c r="B15" s="1" cm="1">
         <f t="array" aca="1" ref="B15:E15" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1">
         <f ca="1"/>
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D15" s="1">
         <f ca="1"/>
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="E15" s="1">
         <f ca="1"/>
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" si="4"/>
@@ -5081,19 +5081,19 @@
       </c>
       <c r="B16" s="1" cm="1">
         <f t="array" aca="1" ref="B16:E16" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C16" s="1">
         <f ca="1"/>
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D16" s="1">
         <f ca="1"/>
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E16" s="1">
         <f ca="1"/>
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="G16" s="1">
         <f t="shared" si="4"/>
@@ -5344,19 +5344,19 @@
       </c>
       <c r="B17" s="1" cm="1">
         <f t="array" aca="1" ref="B17:E17" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1">
         <f ca="1"/>
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D17" s="1">
         <f ca="1"/>
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E17" s="1">
         <f ca="1"/>
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" si="4"/>
@@ -5607,19 +5607,19 @@
       </c>
       <c r="B18" s="1" cm="1">
         <f t="array" aca="1" ref="B18:E18" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C18" s="1">
         <f ca="1"/>
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D18" s="1">
         <f ca="1"/>
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E18" s="1">
         <f ca="1"/>
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" si="4"/>
@@ -5870,19 +5870,19 @@
       </c>
       <c r="B19" s="1" cm="1">
         <f t="array" aca="1" ref="B19:E19" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C19" s="1">
         <f ca="1"/>
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D19" s="1">
         <f ca="1"/>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E19" s="1">
         <f ca="1"/>
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" si="4"/>
@@ -6133,19 +6133,19 @@
       </c>
       <c r="B20" s="1" cm="1">
         <f t="array" aca="1" ref="B20:E20" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C20" s="1">
         <f ca="1"/>
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="D20" s="1">
         <f ca="1"/>
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E20" s="1">
         <f ca="1"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" si="4"/>
@@ -6396,19 +6396,19 @@
       </c>
       <c r="B21" s="1" cm="1">
         <f t="array" aca="1" ref="B21:E21" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C21" s="1">
         <f ca="1"/>
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D21" s="1">
         <f ca="1"/>
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="E21" s="1">
         <f ca="1"/>
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="G21" s="1">
         <f t="shared" si="4"/>
@@ -6659,19 +6659,19 @@
       </c>
       <c r="B22" s="1" cm="1">
         <f t="array" aca="1" ref="B22:E22" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C22" s="1">
         <f ca="1"/>
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D22" s="1">
         <f ca="1"/>
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E22" s="1">
         <f ca="1"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G22" s="1">
         <f t="shared" si="4"/>
@@ -6922,19 +6922,19 @@
       </c>
       <c r="B23" s="1" cm="1">
         <f t="array" aca="1" ref="B23:E23" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C23" s="1">
         <f ca="1"/>
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D23" s="1">
         <f ca="1"/>
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="E23" s="1">
         <f ca="1"/>
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="N23" s="1">
         <v>40001</v>
@@ -7168,19 +7168,19 @@
       </c>
       <c r="B24" s="1" cm="1">
         <f t="array" aca="1" ref="B24:E24" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="C24" s="1">
         <f ca="1"/>
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D24" s="1">
         <f ca="1"/>
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E24" s="1">
         <f ca="1"/>
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="N24" s="1">
         <v>40001</v>
@@ -7414,19 +7414,19 @@
       </c>
       <c r="B25" s="1" cm="1">
         <f t="array" aca="1" ref="B25:E25" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C25" s="1">
         <f ca="1"/>
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="D25" s="1">
         <f ca="1"/>
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="E25" s="1">
         <f ca="1"/>
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N25" s="1">
         <v>40001</v>
@@ -7660,19 +7660,19 @@
       </c>
       <c r="B26" s="1" cm="1">
         <f t="array" aca="1" ref="B26:E26" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C26" s="1">
         <f ca="1"/>
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D26" s="1">
         <f ca="1"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E26" s="1">
         <f ca="1"/>
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="N26" s="1">
         <v>40001</v>
@@ -7906,19 +7906,19 @@
       </c>
       <c r="B27" s="1" cm="1">
         <f t="array" aca="1" ref="B27:E27" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="C27" s="1">
         <f ca="1"/>
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D27" s="1">
         <f ca="1"/>
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E27" s="1">
         <f ca="1"/>
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="N27" s="1">
         <v>40001</v>
@@ -8156,15 +8156,15 @@
       </c>
       <c r="C28" s="1">
         <f ca="1"/>
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="D28" s="1">
         <f ca="1"/>
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="E28" s="1">
         <f ca="1"/>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N28" s="1">
         <v>40001</v>
@@ -8402,11 +8402,11 @@
       </c>
       <c r="C29" s="1">
         <f ca="1"/>
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="D29" s="1">
         <f ca="1"/>
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="E29" s="1">
         <f ca="1"/>
@@ -8644,19 +8644,19 @@
       </c>
       <c r="B30" s="1" cm="1">
         <f t="array" aca="1" ref="B30:E30" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C30" s="1">
         <f ca="1"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D30" s="1">
         <f ca="1"/>
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E30" s="1">
         <f ca="1"/>
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="N30" s="1">
         <v>40001</v>
@@ -8890,19 +8890,19 @@
       </c>
       <c r="B31" s="1" cm="1">
         <f t="array" aca="1" ref="B31:E31" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C31" s="1">
         <f ca="1"/>
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D31" s="1">
         <f ca="1"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E31" s="1">
         <f ca="1"/>
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="N31" s="1">
         <v>40001</v>
@@ -9136,19 +9136,19 @@
       </c>
       <c r="B32" s="1" cm="1">
         <f t="array" aca="1" ref="B32:E32" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="C32" s="1">
         <f ca="1"/>
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D32" s="1">
         <f ca="1"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E32" s="1">
         <f ca="1"/>
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N32" s="1">
         <v>40001</v>
@@ -9382,19 +9382,19 @@
       </c>
       <c r="B33" s="1" cm="1">
         <f t="array" aca="1" ref="B33:E33" ca="1">_xlfn.RANDARRAY(1,4,1,50,TRUE)</f>
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C33" s="1">
         <f ca="1"/>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D33" s="1">
         <f ca="1"/>
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E33" s="1">
         <f ca="1"/>
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="N33" s="1">
         <v>40001</v>
